--- a/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-CLS-08_集計_クラス詳細設計書.xlsx
+++ b/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-CLS-08_集計_クラス詳細設計書.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：22 本のオンライン詳細設計書（ONL-001〜022）と 3 本のバッチ詳細設計書（BAT-001〜003）の規格 JSON をクラス単位に集約・再構成したもの。同一クラスのメソッドを複数 ONL / BAT が定義・追記している場合は統合し、重複を除いた。v2.0 で解消した食い違いと、なお残る食い違いは 4. に整理した。</t>
+          <t>本書の位置づけ：23 本のオンライン詳細設計書（ONL-001〜023）と 3 本のバッチ詳細設計書（BAT-001〜003）の規格 JSON、および実コードから起こした API-024〜026（ONL-024〜026。休憩・離席の打刻、部署一覧。専用の ONL 詳細設計書は未作成）を、クラス単位に集約・再構成したもの。同一クラスのメソッドを複数 ONL / BAT が定義・追記している場合は統合し、重複を除いた。解消した食い違いと、なお残る食い違い（実コード照合の結果を含む）は 4. に整理した。</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1135,7 +1135,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>レスポンス項目の定義（ONL-018 4.2 JSON パス接頭辞 rows[]. を除いた項目）</t>
+          <t>record 宣言のコンポーネント（実コード dto/MonthlyReportRow.java）</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
@@ -1147,24 +1147,20 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>項目名</t>
+          <t>コンポーネント</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>論理名</t>
+          <t>型</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>編集内容</t>
-        </is>
-      </c>
+          <t>注釈（検証・Jackson）</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="9" t="n"/>
     </row>
@@ -1176,19 +1172,15 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>社員ID</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="9" t="n"/>
     </row>
@@ -1200,19 +1192,15 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>氏名</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>users.name</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="9" t="n"/>
     </row>
@@ -1224,19 +1212,15 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>部署名</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>departments.name。部署未設定は null</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
@@ -1248,23 +1232,19 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>出勤日数</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>出勤打刻（clock_in）のある日数。0 以上</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="9" t="n"/>
     </row>
-    <row r="31" ht="34" customHeight="1">
+    <row r="31" ht="19" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>workMinutes</t>
@@ -1272,19 +1252,15 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>総勤務時間（分）</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>attendance_records.work_minutes の合計。H:mm 表示は画面側で変換（例 6930 → 115:30）</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="9" t="n"/>
     </row>
@@ -1296,23 +1272,19 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>残業時間（分）</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>attendance_records.overtime_minutes の合計</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="9" t="n"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="19" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>leaveDays</t>
@@ -1320,83 +1292,283 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>休暇取得日数</t>
+          <t>BigDecimal</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>承認済み（APPROVED）の休暇申請の days 合計。開始日が対象月の申請を計上。小数第1位（0.5 日単位）</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="9" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>④ クラス不変条件・排他・留意点</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>レスポンス項目の定義（ONL-018 4.2 JSON パス接頭辞 rows[]. を除いた項目）</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>編集内容</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="9" t="n"/>
     </row>
-    <row r="36" ht="49" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>userId</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>社員ID</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>userName</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>users.name</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>departmentName</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>部署名</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>departments.name。部署未設定は null</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="9" t="n"/>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>workDays</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>出勤日数</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>出勤打刻（clock_in）のある日数。0 以上</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>workMinutes</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>総勤務時間（分）</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>attendance_records.work_minutes の合計。H:mm 表示は画面側で変換（例 6930 → 115:30）</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="9" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>overtimeMinutes</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>残業時間（分）</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>attendance_records.overtime_minutes の合計</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>leaveDays</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>休暇取得日数</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>承認済み（APPROVED）の休暇申請の days 合計。開始日が対象月の申請を計上。小数第1位（0.5 日単位）</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>④ クラス不変条件・排他・留意点</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="9" t="n"/>
+    </row>
+    <row r="45" ht="49" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>設計原則（このクラス種別）</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>・record（不変）。コンポーネント名がそのまま JSON キー（camelCase）。
 ・null の項目も出力する（spring.jackson.default-property-inclusion を non_null にしない）。
 ・配列は 0 件でも [] を返す（null にしない）。</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>⑤ 付帯情報（ONL の補足表・定義コード）</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>ONL-018 DTO 定義（dto/MonthlyReportResponse.java, dto/MonthlyReportRow.java）</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="9" t="n"/>
-    </row>
-    <row r="40" ht="79" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
+    </row>
+    <row r="49" ht="79" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>public record MonthlyReportRow(Long userId, String userName, String departmentName,
     long workDays, long workMinutes, long overtimeMinutes, BigDecimal leaveDays) {}
@@ -1405,77 +1577,86 @@
 ※ MonthlyReportRow は ONL-020 の rows[] でも使用する。</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="9" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>テスト観点</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>DTO は値保持のみ。Controller の MockMvc テスト（JSON キー・null 出力・検証アノテーション）で検証する。</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="9" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="46">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="D27:F27"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D39:F39"/>
     <mergeCell ref="B17:F17"/>
-    <mergeCell ref="D33:F33"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D38:F38"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="D31:F31"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1489,7 +1670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1842,7 +2023,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>レスポンス項目の定義（ONL-020 4.2 ）</t>
+          <t>record 宣言のコンポーネント（実コード dto/SubordinateSummaryResponse.java）</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -1854,24 +2035,20 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>項目名</t>
+          <t>コンポーネント</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>論理名</t>
+          <t>型</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>編集内容</t>
-        </is>
-      </c>
+          <t>注釈（検証・Jackson）</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="9" t="n"/>
     </row>
@@ -1883,103 +2060,83 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>対象月</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>正規化した yyyy-MM</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="9" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>rows[]</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>部下別集計</t>
+          <t>List&lt;MonthlyReportRow&gt;</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>社員ID 昇順。部下がいない場合は空配列（エラーにしない）</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="9" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>rows[].userId</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>社員ID</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>レスポンス項目の定義（ONL-020 4.2 ）</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="9" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>rows[].userName</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>users.name</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>編集内容</t>
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
-    <row r="30" ht="34" customHeight="1">
+    <row r="30" ht="19" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>rows[].departmentName</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>部署名</t>
+          <t>対象月</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1989,7 +2146,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>departments.name（SCR-203 では未表示。ONL-018 と DTO を共用するため返す）。未設定は null</t>
+          <t>正規化した yyyy-MM</t>
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1998,22 +2155,22 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>rows[].workDays</t>
+          <t>rows[]</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>出勤日数</t>
+          <t>部下別集計</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>clock_in のある日数</t>
+          <t>社員ID 昇順。部下がいない場合は空配列（エラーにしない）</t>
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -2022,12 +2179,12 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>rows[].workMinutes</t>
+          <t>rows[].userId</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>総勤務時間（分）</t>
+          <t>社員ID</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2037,106 +2194,160 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>work_minutes の合計。H:mm 表示は画面側</t>
+          <t>users.id</t>
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="9" t="n"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="19" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>rows[].overtimeMinutes</t>
+          <t>rows[].userName</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>残業時間（分）</t>
+          <t>氏名</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>overtime_minutes の合計</t>
+          <t>users.name</t>
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="9" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>rows[].leaveDays</t>
+          <t>rows[].departmentName</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>休暇取得日数</t>
+          <t>部署名</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>承認済み休暇申請の days 合計（開始日が対象月内）。小数第1位</t>
+          <t>departments.name（SCR-203 では未表示。ONL-018 と DTO を共用するため返す）。未設定は null</t>
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="9" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>④ クラス不変条件・排他・留意点</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>rows[].workDays</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>出勤日数</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>clock_in のある日数</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>rows[].workMinutes</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>総勤務時間（分）</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>work_minutes の合計。H:mm 表示は画面側</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="9" t="n"/>
     </row>
-    <row r="37" ht="49" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>設計原則（このクラス種別）</t>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>rows[].overtimeMinutes</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>・record（不変）。コンポーネント名がそのまま JSON キー（camelCase）。
-・null の項目も出力する（spring.jackson.default-property-inclusion を non_null にしない）。
-・配列は 0 件でも [] を返す（null にしない）。</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
+          <t>残業時間（分）</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>overtime_minutes の合計</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="9" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>⑤ 付帯情報（ONL の補足表・定義コード）</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="9" t="n"/>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>ONL-020 DTO 定義（dto/SubordinateSummaryResponse.java）</t>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>rows[].leaveDays</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>休暇取得日数</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>承認済み休暇申請の days 合計（開始日が対象月内）。小数第1位</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>④ クラス不変条件・排他・留意点</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
@@ -2148,13 +2359,14 @@
     <row r="41" ht="49" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>public record SubordinateSummaryResponse(String month, List&lt;MonthlyReportRow&gt; rows) {}
-※ MonthlyReportRow は ONL-018 の定義（userId, userName, departmentName, workDays, workMinutes, overtimeMinutes, leaveDays）を使用。</t>
+          <t>設計原則（このクラス種別）</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>・record（不変）。コンポーネント名がそのまま JSON キー（camelCase）。
+・null の項目も出力する（spring.jackson.default-property-inclusion を non_null にしない）。
+・配列は 0 件でも [] を返す（null にしない）。</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -2165,7 +2377,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
+          <t>⑤ 付帯情報（ONL の補足表・定義コード）</t>
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
@@ -2175,60 +2387,105 @@
       <c r="F43" s="9" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>DTO は値保持のみ。Controller の MockMvc テスト（JSON キー・null 出力・検証アノテーション）で検証する。</t>
-        </is>
-      </c>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>ONL-020 DTO 定義（dto/SubordinateSummaryResponse.java）</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="9" t="n"/>
     </row>
+    <row r="45" ht="49" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>public record SubordinateSummaryResponse(String month, List&lt;MonthlyReportRow&gt; rows) {}
+※ MonthlyReportRow は ONL-018 の定義（userId, userName, departmentName, workDays, workMinutes, overtimeMinutes, leaveDays）を使用。</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>DTO は値保持のみ。Controller の MockMvc テスト（JSON キー・null 出力・検証アノテーション）で検証する。</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="42">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="D27:F27"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="D25:F25"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="C21:D21"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="D34:F34"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2256,7 +2513,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>4.1 解消済み（v2.0）：更新済み規格で是正された食い違い（前版の報告分。規格 JSON を機械照合して確認）</t>
+          <t>4.1 解消済み：規格の更新・実装反映で是正された食い違い（前版までの報告分。規格 JSON と実コードを照合して確認）</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
@@ -2288,7 +2545,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>v2.0 の状態</t>
+          <t>現在の状態</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -2312,7 +2569,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>4.2 未決事項・残る食い違い（v2.0 の検証で新たに見つかったもの／外部文書の課題）</t>
+          <t>4.2 未決事項・残る食い違い（実コード照合で確認した設計↔実装の差異／規格間の差異／外部文書の課題）</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -2381,7 +2638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2463,6 +2720,52 @@
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="79" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>実コードとの全面照合（コードが唯一の正）：メソッドの処理（疑似コード）を実コードの本体に置換（コードと乖離していたもの）、シグネチャ（引数名・修飾子）・コンストラクタ依存・Repository のクエリ記述を実装に合わせて訂正。該当クラスのトークン無効化・INACTIVE の扱いの記述を ActiveUserFilter 実装後の内容に更新</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="49" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>実コード再照合（2026/10/05 夜）：本領域のクラスに変更なし。部署プルダウンを部署一覧 API（API-026、領域 07）から取得する画面側の変更のみ（本領域の API は変更なし）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3571,7 +3874,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -3631,7 +3934,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
+    <row r="35" ht="49" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>1. monthly</t>
@@ -3639,7 +3942,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>public ResponseEntity&lt;?&gt; monthly( String month, Long departmentId, String format, Jwt jwt)</t>
+          <t>public ResponseEntity&lt;?&gt; monthly( String month, Long departmentId, String format, Authentication auth)</t>
         </is>
       </c>
       <c r="C35" s="9" t="n"/>
@@ -3708,7 +4011,7 @@
       <c r="B39" s="15" t="inlineStr">
         <is>
           <t>@GetMapping("/monthly")
-public ResponseEntity&lt;?&gt; monthly( @RequestParam(required = false) String month, @RequestParam(required = false) Long departmentId, @RequestParam(required = false, defaultValue = "json") String format, @AuthenticationPrincipal Jwt jwt)</t>
+public ResponseEntity&lt;?&gt; monthly( @RequestParam(required = false) String month, @RequestParam(required = false) Long departmentId, @RequestParam(required = false, defaultValue = "json") String format, Authentication auth)</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -3832,17 +4135,17 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>@AuthenticationPrincipal。CSV 出力ログの操作者 ID（sub）用</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D46" s="8" t="n"/>
@@ -3913,7 +4216,7 @@
 if (!csv) return ResponseEntity.ok(res);                  // ⑦ No
 byte[] body = reportService.toCsv(res);                   // ⑧
 log.info("Monthly report exported month={} departmentId={} rows={} by={}",
-    ym, departmentId, res.rows().size(), Long.valueOf(jwt.getSubject()));
+    ym, departmentId, res.rows().size(), Long.valueOf(auth.getName()));
 return ResponseEntity.ok()                                // ⑨
     .contentType(new MediaType("text", "csv", StandardCharsets.UTF_8))
     .header(HttpHeaders.CONTENT_DISPOSITION, ContentDisposition.attachment()
@@ -4809,7 +5112,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -4877,7 +5180,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>public SubordinateSummaryResponse subordinatesSummary( String month, Jwt jwt)</t>
+          <t>public SubordinateSummaryResponse subordinatesSummary( String month, Authentication auth)</t>
         </is>
       </c>
       <c r="C35" s="9" t="n"/>
@@ -4937,7 +5240,7 @@
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="9" t="n"/>
     </row>
-    <row r="39" ht="49" customHeight="1">
+    <row r="39" ht="34" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -4946,7 +5249,7 @@
       <c r="B39" s="15" t="inlineStr">
         <is>
           <t>@GetMapping("/subordinates/summary")
-public SubordinateSummaryResponse subordinatesSummary( @RequestParam(required = false) String month, @AuthenticationPrincipal Jwt jwt)</t>
+public SubordinateSummaryResponse subordinatesSummary( @RequestParam(required = false) String month, Authentication auth)</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
@@ -5030,17 +5333,17 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>@AuthenticationPrincipal。sub = ログイン上長の users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -5104,7 +5407,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Long managerId = Long.valueOf(jwt.getSubject());          // ③
+          <t>Long managerId = Long.valueOf(auth.getName());          // ③
 return reportService.subordinates(managerId, month);       // ④〜⑦</t>
         </is>
       </c>
@@ -6015,7 +6318,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -6195,7 +6498,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>private static String csvCell(String v)</t>
+          <t>static String csvCell(String v)</t>
         </is>
       </c>
       <c r="C38" s="9" t="n"/>
@@ -6804,7 +7107,7 @@
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="9" t="n"/>
     </row>
-    <row r="71" ht="94" customHeight="1">
+    <row r="71" ht="64" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
           <t>処理詳細（疑似コード）</t>
@@ -6812,12 +7115,10 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>LocalDate from = ym.atDay(1);                              // ④ 月初
-LocalDate to   = ym.atEndOfMonth();                        // ④ 月末（うるう年は atEndOfMonth が処理）
-List&lt;Object[]&gt; raw = reportRepository.findMonthlySummary(
-        from, to, departmentId, null);                     // ⑤ managerId=null → 全社
-List&lt;MonthlyReportRow&gt; rows = toRows(raw);                 // ⑥
-return new MonthlyReportResponse(ym.toString(), departmentId, rows);   // ym.toString() = "2026-10"</t>
+          <t>LocalDate from = ym.atDay(1);
+LocalDate to = ym.atEndOfMonth();
+List&lt;Object[]&gt; raw = reportRepository.findMonthlySummary(from, to, departmentId, null);
+return new MonthlyReportResponse(ym.toString(), departmentId, toRows(raw));</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -7182,7 +7483,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>private static String csvCell(String v)
+          <t>static String csvCell(String v)
 public String csvFileName(YearMonth ym)
 static String formatHm(long minutes)
 public byte[] toCsv(MonthlyReportResponse res)</t>
@@ -7664,7 +7965,7 @@
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="9" t="n"/>
     </row>
-    <row r="120" ht="124" customHeight="1">
+    <row r="120" ht="64" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
         <is>
           <t>処理詳細（疑似コード）</t>
@@ -7672,14 +7973,10 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Objects.requireNonNull(managerId, "managerId");           // null だと全社集計になってしまうため必須
-YearMonth ym = parseMonth(month);                         // ② E-002
-LocalDate from = ym.atDay(1);                             // ④
-LocalDate to   = ym.atEndOfMonth();
-List&lt;Object[]&gt; raw = reportRepository.findMonthlySummary(
-        from, to, null, managerId);                        // ⑤ departmentId=null, managerId=自分
-List&lt;MonthlyReportRow&gt; rows = toRows(raw);                 // ⑥（ONL-018 と共用）
-return new SubordinateSummaryResponse(ym.toString(), rows);// ⑦</t>
+          <t>Objects.requireNonNull(managerId, "managerId");
+YearMonth ym = parseMonth(month);
+List&lt;Object[]&gt; raw = reportRepository.findMonthlySummary(ym.atDay(1), ym.atEndOfMonth(), null, managerId);
+return new SubordinateSummaryResponse(ym.toString(), toRows(raw));</t>
         </is>
       </c>
       <c r="C120" s="8" t="n"/>
@@ -9901,7 +10198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10254,7 +10551,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>レスポンス項目の定義（ONL-018 4.2 最上位の項目（要素 DTO の項目は各 DTO を参照））</t>
+          <t>record 宣言のコンポーネント（実コード dto/MonthlyReportResponse.java）</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -10266,24 +10563,20 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>項目名</t>
+          <t>コンポーネント</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>論理名</t>
+          <t>型</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>編集内容</t>
-        </is>
-      </c>
+          <t>注釈（検証・Jackson）</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="9" t="n"/>
     </row>
@@ -10295,19 +10588,15 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>対象月</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>リクエストの month を正規化した yyyy-MM</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="9" t="n"/>
     </row>
@@ -10319,131 +10608,231 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>部署ID</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>絞込指定がなければ null</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="9" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>rows[]</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>社員別集計</t>
+          <t>List&lt;MonthlyReportRow&gt;</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>部署ID 昇順（部署未設定は最後）→ 社員ID 昇順。0 件なら空配列</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="9" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>【format=csv】本文</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>CSV ファイル</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>text/csv</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>UTF-8（BOM 付き）。列は RPT-001（下記エラー例の下の CSV 例）。Content-Disposition: attachment; filename="kintai_summary_yyyymm.csv"</t>
-        </is>
-      </c>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>レスポンス項目の定義（ONL-018 4.2 最上位の項目（要素 DTO の項目は各 DTO を参照））</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>④ クラス不変条件・排他・留意点</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>編集内容</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>対象月</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>リクエストの month を正規化した yyyy-MM</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="9" t="n"/>
     </row>
-    <row r="32" ht="49" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>departmentId</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>部署ID</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>絞込指定がなければ null</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>rows[]</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>社員別集計</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>部署ID 昇順（部署未設定は最後）→ 社員ID 昇順。0 件なら空配列</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>【format=csv】本文</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>CSV ファイル</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>text/csv</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>UTF-8（BOM 付き）。列は RPT-001（下記エラー例の下の CSV 例）。Content-Disposition: attachment; filename="kintai_summary_yyyymm.csv"</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>④ クラス不変条件・排他・留意点</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="49" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>設計原則（このクラス種別）</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>・record（不変）。コンポーネント名がそのまま JSON キー（camelCase）。
 ・null の項目も出力する（spring.jackson.default-property-inclusion を non_null にしない）。
 ・配列は 0 件でも [] を返す（null にしない）。</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>⑤ 付帯情報（ONL の補足表・定義コード）</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="9" t="n"/>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>ONL-018 DTO 定義（dto/MonthlyReportResponse.java, dto/MonthlyReportRow.java）</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="79" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="9" t="n"/>
+    </row>
+    <row r="41" ht="79" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>public record MonthlyReportRow(Long userId, String userName, String departmentName,
     long workDays, long workMinutes, long overtimeMinutes, BigDecimal leaveDays) {}
@@ -10452,74 +10841,79 @@
 ※ MonthlyReportRow は ONL-020 の rows[] でも使用する。</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>テスト観点</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>DTO は値保持のみ。Controller の MockMvc テスト（JSON キー・null 出力・検証アノテーション）で検証する。</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="9" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="38">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="D27:F27"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A35:F35"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
